--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/05_model_comparison_all/outputs/model_comparison_all_w2w2_w2w3.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/05_model_comparison_all/outputs/model_comparison_all_w2w2_w2w3.xlsx
@@ -451,9 +451,9 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -574,17 +574,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>original_groups_drop_groups</t>
+          <t>original_groups_no_drop</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -596,31 +596,31 @@
         <v>6603</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.7903116268695702</v>
+        <v>0.8229239746123514</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.7167937512903448</v>
+        <v>0.7464748927580116</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.7405651760492677</v>
+        <v>0.7690985626292267</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.7344224411911611</v>
+        <v>0.7585175333171889</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.746914091495097</v>
+        <v>0.7801879126460133</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.7976597659765977</v>
+        <v>0.8304599690738305</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.7221801665404997</v>
+        <v>0.753217259651779</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.743893928820656</v>
+        <v>0.7745504840940526</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>original_groups_no_drop</t>
+          <t>original_groups_drop_groups</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -668,31 +668,31 @@
         <v>6603</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.8229239746123514</v>
+        <v>0.7903116268695702</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.7464748927580116</v>
+        <v>0.7167937512903448</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.7690985626292267</v>
+        <v>0.7405651760492677</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.7585175333171889</v>
+        <v>0.7344224411911611</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.7801879126460133</v>
+        <v>0.746914091495097</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.8304599690738305</v>
+        <v>0.7976597659765977</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.753217259651779</v>
+        <v>0.7221801665404997</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.7745504840940526</v>
+        <v>0.743893928820656</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -740,31 +740,31 @@
         <v>6603</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.734</v>
+        <v>0.741</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.755</v>
+        <v>0.761</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -812,31 +812,31 @@
         <v>6603</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.8106423133969024</v>
+        <v>0.8196197852234338</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.7340574174752827</v>
+        <v>0.7404201362604088</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.7553490746860423</v>
+        <v>0.7603958222391946</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.752439761767649</v>
+        <v>0.7597800250668976</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7583787162558112</v>
+        <v>0.7611743563698872</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.8170070853239171</v>
+        <v>0.8319670428581319</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.7418622255866768</v>
+        <v>0.7426192278576835</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.7643400138217</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -884,31 +884,31 @@
         <v>6603</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.8107380738521348</v>
+        <v>0.8196304550378182</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.734967425962884</v>
+        <v>0.7402682770169523</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.7567322838522765</v>
+        <v>0.7606541839905891</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.7521797362839285</v>
+        <v>0.7588996885343929</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7614556393327343</v>
+        <v>0.7625733484392703</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.8168224514759168</v>
+        <v>0.8320247409356321</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.7373202119606359</v>
+        <v>0.74110522331567</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7611837577426015</v>
+        <v>0.7618384401114207</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         <v>6603</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.766942467087923</v>
+        <v>0.7661410018969599</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7415384615384615</v>
+        <v>0.7468531468531469</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
@@ -1006,17 +1006,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>original_groups_drop_groups</t>
+          <t>original_groups_no_drop</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1028,31 +1028,31 @@
         <v>6603</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.6975036254088497</v>
+        <v>0.7141289146474757</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.6425903241346088</v>
+        <v>0.657581492441447</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.6663594765005694</v>
+        <v>0.6805264313647608</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.654750782622697</v>
+        <v>0.6684021387346073</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.678474073766923</v>
+        <v>0.693147430182655</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.7110993633208449</v>
+        <v>0.7288781115682533</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.6570779712339136</v>
+        <v>0.6744890234670704</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.6780383795309168</v>
+        <v>0.6950354609929078</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>original_groups_no_drop</t>
+          <t>original_groups_drop_groups</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1100,31 +1100,31 @@
         <v>6603</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.7141289146474757</v>
+        <v>0.6975036254088497</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.657581492441447</v>
+        <v>0.6425903241346088</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.6805264313647608</v>
+        <v>0.6663594765005694</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.6684021387346073</v>
+        <v>0.654750782622697</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.693147430182655</v>
+        <v>0.678474073766923</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.7288781115682533</v>
+        <v>0.7110993633208449</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.6744890234670704</v>
+        <v>0.6570779712339136</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.6950354609929078</v>
+        <v>0.6780383795309168</v>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
@@ -1172,22 +1172,22 @@
         <v>6603</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.65</v>
+        <v>0.649</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.669</v>
+        <v>0.668</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.666</v>
+        <v>0.664</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.673</v>
+        <v>0.672</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.717</v>
@@ -1196,7 +1196,7 @@
         <v>0.656</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.676</v>
+        <v>0.675</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
@@ -1244,31 +1244,31 @@
         <v>6603</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.7071292704983907</v>
+        <v>0.7099569243042742</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.6501624113963251</v>
+        <v>0.6513746473057601</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.6696133289017522</v>
+        <v>0.6708998877631803</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.6654255427530236</v>
+        <v>0.6663409082623397</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.673867683950822</v>
+        <v>0.675599693156138</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.7174086928540235</v>
+        <v>0.7179350449352977</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.6525359576078729</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6719085060757684</v>
+        <v>0.6742857142857143</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1316,31 +1316,31 @@
         <v>6603</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.7073519039995486</v>
+        <v>0.7100636559204856</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.6489509783680867</v>
+        <v>0.6507684720023856</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.6684607619169196</v>
+        <v>0.6710782008674138</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.664276158654306</v>
+        <v>0.665022039177015</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.672717019467999</v>
+        <v>0.6773258972073062</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.7176638242121958</v>
+        <v>0.7178522996299446</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.6563209689629069</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.6757142857142857</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -1388,31 +1388,31 @@
         <v>6603</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.6625443441404723</v>
+        <v>0.6580855247737147</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.663021582733813</v>
+        <v>0.6517985611510791</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GNN</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GraphSAGE</t>
+          <t>Decomposed Logistic</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -1653,57 +1653,57 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition_plus_graph_edges</t>
+          <t>drop_plus_decomposition</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
+          <t>Drop + decomposition features</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5-seed heldout test mean</t>
+          <t>CV5 mean</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.819</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.741</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.761</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.766942467087923</v>
+        <v>0.762</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.7415384615384615</v>
+        <v>0.759</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.831</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.745</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.766</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>w2_self</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Ridge Logistic</t>
+          <t>LASSO Logistic</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -1745,31 +1745,31 @@
         <v>6603</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.8107380738521348</v>
+        <v>0.8196197852234338</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.734967425962884</v>
+        <v>0.7404201362604088</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.7567322838522765</v>
+        <v>0.7603958222391946</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.7521797362839285</v>
+        <v>0.7597800250668976</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.7614556393327343</v>
+        <v>0.7611743563698872</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.8168224514759168</v>
+        <v>0.8319670428581319</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.7373202119606359</v>
+        <v>0.7426192278576835</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7611837577426015</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>LASSO Logistic</t>
+          <t>Ridge Logistic</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1820,31 +1820,31 @@
         <v>6603</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.8106423133969024</v>
+        <v>0.8196304550378182</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.7340574174752827</v>
+        <v>0.7402682770169523</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.7553490746860423</v>
+        <v>0.7606541839905891</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.752439761767649</v>
+        <v>0.7588996885343929</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.7583787162558112</v>
+        <v>0.7625733484392703</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.8170070853239171</v>
+        <v>0.8320247409356321</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.7418622255866768</v>
+        <v>0.74110522331567</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7643400138217</v>
+        <v>0.7618384401114207</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>GNN</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Decomposed Logistic</t>
+          <t>GraphSAGE</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1878,57 +1878,57 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition</t>
+          <t>drop_plus_decomposition_plus_graph_edges</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition features</t>
+          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>CV5 mean</t>
+          <t>5-seed heldout test mean</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.734</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.755</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.752</v>
+        <v>0.7661410018969599</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.758</v>
+        <v>0.7468531468531469</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.74</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.762</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w2</t>
+          <t>w2_self</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2120,31 +2120,31 @@
         <v>6603</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.7071292704983907</v>
+        <v>0.7099569243042742</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.6501624113963251</v>
+        <v>0.6513746473057601</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.6696133289017522</v>
+        <v>0.6708998877631803</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.6654255427530236</v>
+        <v>0.6663409082623397</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.673867683950822</v>
+        <v>0.675599693156138</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.7174086928540235</v>
+        <v>0.7179350449352977</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.6525359576078729</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.6719085060757684</v>
+        <v>0.6742857142857143</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>Regularized logistic</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Decomposed Logistic</t>
+          <t>Ridge Logistic</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -2195,31 +2195,31 @@
         <v>6603</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.707</v>
+        <v>0.7100636559204856</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.65</v>
+        <v>0.6507684720023856</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.669</v>
+        <v>0.6710782008674138</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.666</v>
+        <v>0.665022039177015</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.673</v>
+        <v>0.6773258972073062</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.717</v>
+        <v>0.7178522996299446</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.656</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.676</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\03_ridge_lasso_regularized\outputs\ridge_lasso_regularized_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Regularized logistic</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Ridge Logistic</t>
+          <t>Decomposed Logistic</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -2270,31 +2270,31 @@
         <v>6603</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.7073519039995486</v>
+        <v>0.71</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.6489509783680867</v>
+        <v>0.649</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.6684607619169196</v>
+        <v>0.668</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.664276158654306</v>
+        <v>0.664</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.672717019467999</v>
+        <v>0.672</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.7176638242121958</v>
+        <v>0.717</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6563209689629069</v>
+        <v>0.656</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.6757142857142857</v>
+        <v>0.675</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\03_ridge_lasso_regularized\outputs\ridge_lasso_regularized_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GNN</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>GraphSAGE</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -2328,48 +2328,48 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition_plus_graph_edges</t>
+          <t>original_groups_drop_groups</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>5-seed heldout test mean</t>
+          <t>CV5 mean</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6975036254088497</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6425903241346088</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6663594765005694</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.6625443441404723</v>
+        <v>0.654750782622697</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.663021582733813</v>
+        <v>0.678474073766923</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.7110993633208449</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6570779712339136</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6780383795309168</v>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\01_logistic_original_groups\outputs\logistic_original_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>GNN</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>GraphSAGE</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -2403,48 +2403,48 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>original_groups_drop_groups</t>
+          <t>drop_plus_decomposition_plus_graph_edges</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>CV5 mean</t>
+          <t>5-seed heldout test mean</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.6975036254088497</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.6425903241346088</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.6663594765005694</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.654750782622697</v>
+        <v>0.6580855247737147</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.678474073766923</v>
+        <v>0.6517985611510791</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.7110993633208449</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.6570779712339136</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0.6780383795309168</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\01_logistic_original_groups\outputs\logistic_original_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2473,10 +2473,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GNN</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GraphSAGE</t>
+          <t>Decomposed Logistic</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -2685,57 +2685,57 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition_plus_graph_edges</t>
+          <t>drop_plus_decomposition</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
+          <t>Drop + decomposition features</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5-seed heldout test mean</t>
+          <t>CV5 mean</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.819</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.741</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.761</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.766942467087923</v>
+        <v>0.762</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.7415384615384615</v>
+        <v>0.759</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.831</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.745</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.766</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>w2_self</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Ridge Logistic</t>
+          <t>LASSO Logistic</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -2777,31 +2777,31 @@
         <v>6603</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.8107380738521348</v>
+        <v>0.8196197852234338</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.734967425962884</v>
+        <v>0.7404201362604088</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.7567322838522765</v>
+        <v>0.7603958222391946</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.7521797362839285</v>
+        <v>0.7597800250668976</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.7614556393327343</v>
+        <v>0.7611743563698872</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.8168224514759168</v>
+        <v>0.8319670428581319</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.7373202119606359</v>
+        <v>0.7426192278576835</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.7611837577426015</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>LASSO Logistic</t>
+          <t>Ridge Logistic</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -2852,31 +2852,31 @@
         <v>6603</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.8106423133969024</v>
+        <v>0.8196304550378182</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.7340574174752827</v>
+        <v>0.7402682770169523</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.7553490746860423</v>
+        <v>0.7606541839905891</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.752439761767649</v>
+        <v>0.7588996885343929</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.7583787162558112</v>
+        <v>0.7625733484392703</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.8170070853239171</v>
+        <v>0.8320247409356321</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.7418622255866768</v>
+        <v>0.74110522331567</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7643400138217</v>
+        <v>0.7618384401114207</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>GNN</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Decomposed Logistic</t>
+          <t>GraphSAGE</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -2910,57 +2910,57 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition</t>
+          <t>drop_plus_decomposition_plus_graph_edges</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition features</t>
+          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>CV5 mean</t>
+          <t>5-seed heldout test mean</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.734</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.755</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.752</v>
+        <v>0.7661410018969599</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.758</v>
+        <v>0.7468531468531469</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.74</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.762</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w2</t>
+          <t>w2_self</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3055,10 +3055,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -3066,7 +3066,7 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Original/non-decomposed questionnaire groups before planned feature dropping</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -3284,31 +3284,31 @@
         <v>6603</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.7071292704983907</v>
+        <v>0.7099569243042742</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.6501624113963251</v>
+        <v>0.6513746473057601</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.6696133289017522</v>
+        <v>0.6708998877631803</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.6654255427530236</v>
+        <v>0.6663409082623397</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.673867683950822</v>
+        <v>0.675599693156138</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.7174086928540235</v>
+        <v>0.7179350449352977</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.6525359576078729</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.6719085060757684</v>
+        <v>0.6742857142857143</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>Regularized logistic</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Decomposed Logistic</t>
+          <t>Ridge Logistic</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -3359,31 +3359,31 @@
         <v>6603</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.707</v>
+        <v>0.7100636559204856</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.65</v>
+        <v>0.6507684720023856</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.669</v>
+        <v>0.6710782008674138</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.666</v>
+        <v>0.665022039177015</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.673</v>
+        <v>0.6773258972073062</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.717</v>
+        <v>0.7178522996299446</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.656</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.676</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\03_ridge_lasso_regularized\outputs\ridge_lasso_regularized_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Regularized logistic</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Ridge Logistic</t>
+          <t>Decomposed Logistic</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -3434,31 +3434,31 @@
         <v>6603</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.7073519039995486</v>
+        <v>0.71</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.6489509783680867</v>
+        <v>0.649</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.6684607619169196</v>
+        <v>0.668</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.664276158654306</v>
+        <v>0.664</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.672717019467999</v>
+        <v>0.672</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.7176638242121958</v>
+        <v>0.717</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.6563209689629069</v>
+        <v>0.656</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6757142857142857</v>
+        <v>0.675</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\03_ridge_lasso_regularized\outputs\ridge_lasso_regularized_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\02_logistic_decomposed_groups\outputs\logistic_decomposed_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>GNN</t>
+          <t>Logistic baseline</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GraphSAGE</t>
+          <t>Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -3492,48 +3492,48 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>drop_plus_decomposition_plus_graph_edges</t>
+          <t>original_groups_drop_groups</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
+          <t>Original/non-decomposed questionnaire groups after planned feature dropping</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>5-seed heldout test mean</t>
+          <t>CV5 mean</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6975036254088497</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6425903241346088</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6663594765005694</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.6625443441404723</v>
+        <v>0.654750782622697</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.663021582733813</v>
+        <v>0.678474073766923</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.7110993633208449</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.6570779712339136</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6780383795309168</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\01_logistic_original_groups\outputs\logistic_original_groups_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Logistic baseline</t>
+          <t>GNN</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>GraphSAGE</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -3567,48 +3567,48 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>original_groups_drop_groups</t>
+          <t>drop_plus_decomposition_plus_graph_edges</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Original/non-decomposed questionnaire groups</t>
+          <t>Drop + decomposition node features with W2 peer nomination graph edges</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>CV5 mean</t>
+          <t>5-seed heldout test mean</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
         <v>6603</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.6975036254088497</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.6425903241346088</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.6663594765005694</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.654750782622697</v>
+        <v>0.6580855247737147</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.678474073766923</v>
+        <v>0.6517985611510791</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.7110993633208449</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.6570779712339136</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.6780383795309168</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\01_logistic_original_groups\outputs\logistic_original_groups_performance.xlsx</t>
+          <t>C:\Users\user\Desktop\TIGPS_Plan_data\20251229_new_progress\Code\paper_data_newdata\main_paper_results\01_model_performance\04_graphsage_gnn\outputs\graphsage_gnn_performance.xlsx</t>
         </is>
       </c>
     </row>
@@ -3632,35 +3632,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="59" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="53" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="33" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
+    <col width="47" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
+    <col width="57" customWidth="1" min="29" max="29"/>
+    <col width="44" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3686,110 +3691,135 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>AUC - Original-group Logistic</t>
+          <t>AUC - Original-group Logistic (drop selected groups)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>AUC - Original-group Logistic (no drop)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>AUC - Ridge Logistic</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Accuracy - Decomposed Logistic</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Accuracy - GraphSAGE</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Accuracy - LASSO Logistic</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Accuracy - Original-group Logistic</t>
-        </is>
-      </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Accuracy - Original-group Logistic (drop selected groups)</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy - Original-group Logistic (no drop)</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t>Accuracy - Ridge Logistic</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>F1 - Decomposed Logistic</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>F1 - GraphSAGE</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>F1 - LASSO Logistic</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>F1 - Original-group Logistic</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>F1 - Original-group Logistic (drop selected groups)</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>F1 - Original-group Logistic (no drop)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>F1 - Ridge Logistic</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Precision - Decomposed Logistic</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Precision - GraphSAGE</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Precision - LASSO Logistic</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>Precision - Original-group Logistic</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Precision - Original-group Logistic (drop selected groups)</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Precision - Original-group Logistic (no drop)</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Precision - Ridge Logistic</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Recall - Decomposed Logistic</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Recall - GraphSAGE</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Recall - LASSO Logistic</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>Recall - Original-group Logistic</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Recall - Original-group Logistic (drop selected groups)</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>Recall - Original-group Logistic (no drop)</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Recall - Ridge Logistic</t>
         </is>
@@ -3802,79 +3832,94 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.8106423133969024</v>
+        <v>0.8196197852234338</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.7903116268695702</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.8107380738521348</v>
+        <v>0.8229239746123514</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.734</v>
+        <v>0.8196304550378182</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.7380772142316426</v>
+        <v>0.741</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.7340574174752827</v>
+        <v>0.7392884178652537</v>
       </c>
       <c r="J2" s="3" t="n">
+        <v>0.7404201362604088</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>0.7167937512903448</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>0.734967425962884</v>
-      </c>
       <c r="L2" s="3" t="n">
-        <v>0.755</v>
+        <v>0.7464748927580116</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.7402682770169523</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.7553490746860423</v>
+        <v>0.761</v>
       </c>
       <c r="O2" s="3" t="n">
+        <v>0.7561565937029477</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.7603958222391946</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>0.7405651760492677</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>0.7567322838522765</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.752</v>
-      </c>
       <c r="R2" s="3" t="n">
-        <v>0.766942467087923</v>
+        <v>0.7690985626292267</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.752439761767649</v>
+        <v>0.7606541839905891</v>
       </c>
       <c r="T2" s="3" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.7661410018969599</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>0.7597800250668976</v>
+      </c>
+      <c r="W2" s="3" t="n">
         <v>0.7344224411911611</v>
       </c>
-      <c r="U2" s="3" t="n">
-        <v>0.7521797362839285</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>0.7415384615384615</v>
-      </c>
       <c r="X2" s="3" t="n">
-        <v>0.7583787162558112</v>
+        <v>0.7585175333171889</v>
       </c>
       <c r="Y2" s="3" t="n">
+        <v>0.7588996885343929</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>0.7468531468531469</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>0.7611743563698872</v>
+      </c>
+      <c r="AC2" s="3" t="n">
         <v>0.746914091495097</v>
       </c>
-      <c r="Z2" s="3" t="n">
-        <v>0.7614556393327343</v>
+      <c r="AD2" s="3" t="n">
+        <v>0.7801879126460133</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.7625733484392703</v>
       </c>
     </row>
     <row r="3">
@@ -3884,79 +3929,94 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.7071292704983907</v>
+        <v>0.7099569243042742</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.6975036254088497</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7073519039995486</v>
+        <v>0.7141289146474757</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.65</v>
+        <v>0.7100636559204856</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.645117335352006</v>
+        <v>0.649</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.6501624113963251</v>
+        <v>0.6386071158213474</v>
       </c>
       <c r="J3" s="3" t="n">
+        <v>0.6513746473057601</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.6425903241346088</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>0.6489509783680867</v>
-      </c>
       <c r="L3" s="3" t="n">
-        <v>0.669</v>
+        <v>0.657581492441447</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6507684720023856</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.6696133289017522</v>
+        <v>0.668</v>
       </c>
       <c r="O3" s="3" t="n">
+        <v>0.6549175423227628</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.6708998877631803</v>
+      </c>
+      <c r="Q3" s="3" t="n">
         <v>0.6663594765005694</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>0.6684607619169196</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.666</v>
-      </c>
       <c r="R3" s="3" t="n">
-        <v>0.6625443441404723</v>
+        <v>0.6805264313647608</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.6654255427530236</v>
+        <v>0.6710782008674138</v>
       </c>
       <c r="T3" s="3" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.6580855247737147</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>0.6663409082623397</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>0.654750782622697</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>0.664276158654306</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>0.663021582733813</v>
-      </c>
       <c r="X3" s="3" t="n">
-        <v>0.673867683950822</v>
+        <v>0.6684021387346073</v>
       </c>
       <c r="Y3" s="3" t="n">
+        <v>0.665022039177015</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>0.6517985611510791</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>0.675599693156138</v>
+      </c>
+      <c r="AC3" s="3" t="n">
         <v>0.678474073766923</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>0.672717019467999</v>
+      <c r="AD3" s="3" t="n">
+        <v>0.693147430182655</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.6773258972073062</v>
       </c>
     </row>
   </sheetData>
@@ -3976,11 +4036,11 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="41" customWidth="1" min="11" max="11"/>
@@ -4050,38 +4110,38 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.8125779501027026</v>
+        <v>0.8187371044796787</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.8229239746123514</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.01034602450964883</v>
+        <v>-0.004186870132672715</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.7539369008475573</v>
+        <v>0.7561565937029477</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.7690985626292267</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.01516166178166944</v>
+        <v>-0.01294196892627897</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.001577950102702563</v>
+        <v>-0.0002628955203212158</v>
       </c>
     </row>
     <row r="3">
@@ -4091,38 +4151,38 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.6994773254878526</v>
+        <v>0.6973820304778542</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.7141289146474757</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.01465158915962317</v>
+        <v>-0.01674688416962156</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.6626631316820681</v>
+        <v>0.6549175423227628</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.6805264313647608</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop)</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.01786329968269262</v>
+        <v>-0.02560888904199798</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.007522674512147387</v>
+        <v>-0.01261796952214578</v>
       </c>
     </row>
   </sheetData>
@@ -4139,7 +4199,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
@@ -4164,7 +4224,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Original-group Logistic</t>
+          <t>Original-group Logistic (no drop and drop selected groups)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
